--- a/Backend/tickets/tagrfid1.xlsx
+++ b/Backend/tickets/tagrfid1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rani_3yana\M-Iot_Backend\Backend\tickets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C6496F-1C0E-4553-8373-551915358AD9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EB21D6-8BA3-4FA5-9CDF-F2EC211BEF97}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{A32A3D01-951C-4AF4-AC72-55E8B68EABA1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>num_serie</t>
   </si>
@@ -36,22 +36,28 @@
     <t>date_install</t>
   </si>
   <si>
-    <t>AF</t>
-  </si>
-  <si>
     <t>actif</t>
   </si>
   <si>
     <t>passif</t>
   </si>
   <si>
-    <t>AT</t>
-  </si>
-  <si>
-    <t>ADG</t>
-  </si>
-  <si>
-    <t>AEE</t>
+    <t>categorie</t>
+  </si>
+  <si>
+    <t>Atc</t>
+  </si>
+  <si>
+    <t>ADGc</t>
+  </si>
+  <si>
+    <t>AEEc</t>
+  </si>
+  <si>
+    <t>Afc</t>
+  </si>
+  <si>
+    <t>Outil</t>
   </si>
 </sst>
 </file>
@@ -404,14 +410,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7073053-EF97-460C-98B1-504BBC0FEB47}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" customWidth="1"/>
     <col min="3" max="3" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -421,49 +427,64 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1">
         <v>45883</v>
       </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>45883</v>
       </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1">
         <v>45883</v>
       </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1">
         <v>45883</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
